--- a/diseases/d050/2026-2029.xlsx
+++ b/diseases/d050/2026-2029.xlsx
@@ -21306,12 +21306,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21336,12 +21336,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N119" t="n">
@@ -21384,40 +21384,185 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW119" t="inlineStr">
+      <c r="AW120" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
+      <c r="AX120" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY119" t="inlineStr">
+      <c r="AY120" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
+      <c r="AZ120" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA119" t="inlineStr">
+      <c r="BA120" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB119" t="inlineStr">
+      <c r="BB120" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC119" t="inlineStr">
+      <c r="BC120" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -21539,7 +21684,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -21549,7 +21694,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d050/2026-2029.xlsx
+++ b/diseases/d050/2026-2029.xlsx
@@ -19005,12 +19005,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -19047,6 +19047,9 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
@@ -19083,42 +19086,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -19150,12 +19153,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -19180,7 +19183,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -19228,42 +19231,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19295,12 +19298,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -19339,9 +19342,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -19350,77 +19350,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19447,7 +19438,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -19499,98 +19490,18 @@
       <c r="P109" t="n">
         <v>0</v>
       </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD109" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG109" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN109" t="b">
-        <v>1</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -19684,17 +19595,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19719,7 +19630,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -19733,76 +19644,168 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="R110" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN110" t="b">
+        <v>1</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -19834,12 +19837,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -19878,9 +19881,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="P111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -19889,77 +19889,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19986,7 +19977,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -20038,98 +20029,18 @@
       <c r="P112" t="n">
         <v>0</v>
       </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -20223,17 +20134,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20258,7 +20169,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -20272,76 +20183,168 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN113" t="b">
+        <v>1</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -20373,12 +20376,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20417,9 +20420,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="P114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -20428,77 +20428,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20525,7 +20516,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -20577,98 +20568,18 @@
       <c r="P115" t="n">
         <v>0</v>
       </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD115" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE115" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF115" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG115" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN115" t="b">
-        <v>1</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -20762,17 +20673,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20797,7 +20708,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -20811,76 +20722,168 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN116" t="b">
+        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -20912,12 +20915,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20956,9 +20959,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -20967,77 +20967,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21064,7 +21055,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -21116,98 +21107,18 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN118" t="b">
-        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -21301,17 +21212,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21336,7 +21247,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -21350,76 +21261,168 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN119" t="b">
+        <v>1</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -21451,12 +21454,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -21481,12 +21484,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N120" t="n">
@@ -21529,40 +21532,579 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW120" t="inlineStr">
+      <c r="AW123" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
+      <c r="AX123" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY120" t="inlineStr">
+      <c r="AY123" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
+      <c r="AZ123" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA120" t="inlineStr">
+      <c r="BA123" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB120" t="inlineStr">
+      <c r="BB123" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC120" t="inlineStr">
+      <c r="BC123" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -21684,7 +22226,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -21694,7 +22236,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -21714,7 +22256,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d050/2026-2029.xlsx
+++ b/diseases/d050/2026-2029.xlsx
@@ -22110,6 +22110,151 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22143,7 +22288,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -22226,7 +22371,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -22236,7 +22381,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d050/2026-2029.xlsx
+++ b/diseases/d050/2026-2029.xlsx
@@ -22255,6 +22255,400 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22371,7 +22765,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -22381,7 +22775,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">
@@ -22401,7 +22795,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d050/2026-2029.xlsx
+++ b/diseases/d050/2026-2029.xlsx
@@ -22649,6 +22649,545 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22682,7 +23221,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -22765,7 +23304,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -22775,7 +23314,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -22795,7 +23334,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d050/2026-2029.xlsx
+++ b/diseases/d050/2026-2029.xlsx
@@ -14110,12 +14110,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -14154,76 +14154,87 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
+        </is>
+      </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -14250,17 +14261,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -14285,7 +14296,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -14299,76 +14310,165 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Official provincial report count for Ebola virus disease; source month is retained and absent rows remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
+        </is>
+      </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -14400,12 +14500,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -14430,7 +14530,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -14444,9 +14544,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -14455,77 +14552,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14552,17 +14640,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -14587,7 +14675,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -14601,168 +14689,76 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD81" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE81" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG81" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN81" t="b">
-        <v>1</v>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14794,12 +14790,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -14824,7 +14820,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -14838,6 +14834,9 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -14846,68 +14845,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -14934,7 +14942,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -14969,7 +14977,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -14986,18 +14994,98 @@
       <c r="P83" t="n">
         <v>0</v>
       </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN83" t="b">
+        <v>1</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -15091,17 +15179,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -15126,7 +15214,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -15140,168 +15228,76 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD84" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE84" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF84" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG84" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN84" t="b">
-        <v>1</v>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ84" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15333,12 +15329,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -15363,7 +15359,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -15377,6 +15373,9 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -15385,68 +15384,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -15473,7 +15481,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -15508,7 +15516,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -15525,18 +15533,98 @@
       <c r="P86" t="n">
         <v>0</v>
       </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN86" t="b">
+        <v>1</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -15630,17 +15718,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -15665,7 +15753,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -15679,168 +15767,76 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD87" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE87" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN87" t="b">
-        <v>1</v>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ87" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15872,12 +15868,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -15902,7 +15898,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -15916,6 +15912,9 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -15924,68 +15923,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -16012,7 +16020,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16047,7 +16055,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -16064,18 +16072,98 @@
       <c r="P89" t="n">
         <v>0</v>
       </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN89" t="b">
+        <v>1</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -16169,17 +16257,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -16204,7 +16292,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -16218,168 +16306,76 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG90" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN90" t="b">
-        <v>1</v>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16411,12 +16407,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -16441,12 +16437,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -16455,7 +16451,7 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
+      <c r="P91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
@@ -16466,68 +16462,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -16554,17 +16559,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -16589,12 +16594,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -16603,76 +16608,168 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN92" t="b">
+        <v>1</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -16704,12 +16801,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -16734,7 +16831,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -16746,6 +16843,9 @@
         <v>0</v>
       </c>
       <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
@@ -16782,17 +16882,17 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -16802,22 +16902,22 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -16849,12 +16949,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -16879,7 +16979,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -16893,20 +16993,19 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -16916,7 +17015,7 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
@@ -16926,55 +17025,55 @@
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
         </is>
       </c>
       <c r="AT94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -17006,12 +17105,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -17036,7 +17135,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -17050,27 +17149,24 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ebola Virus Disease</t>
+          <t>埃博拉出血热</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -17080,12 +17176,12 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
@@ -17095,7 +17191,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr">
@@ -17130,17 +17226,17 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Official provincial report count for Ebola virus disease; source month is retained and absent rows remain unknown.</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -17153,7 +17249,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
@@ -17163,55 +17259,55 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
         </is>
       </c>
       <c r="AT95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -17243,12 +17339,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -17273,7 +17369,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -17287,76 +17383,87 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
+        </is>
+      </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -17383,17 +17490,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -17418,7 +17525,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -17432,21 +17539,98 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="P97" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Official provincial report count for Ebola virus disease; source month is retained and absent rows remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN97" t="b">
+        <v>1</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -17455,7 +17639,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
@@ -17465,55 +17649,55 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
         </is>
       </c>
       <c r="AT97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -17540,17 +17724,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -17575,7 +17759,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -17589,168 +17773,76 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF98" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG98" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN98" t="b">
-        <v>1</v>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17904,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -17957,7 +18049,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -18114,7 +18206,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -18351,7 +18443,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -18466,12 +18558,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18496,7 +18588,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -18510,6 +18602,9 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -18518,68 +18613,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -18606,7 +18710,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -18641,7 +18745,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -18658,18 +18762,98 @@
       <c r="P104" t="n">
         <v>0</v>
       </c>
-      <c r="R104" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN104" t="b">
+        <v>1</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -18763,17 +18947,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -18798,7 +18982,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -18812,168 +18996,76 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD105" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE105" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG105" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN105" t="b">
-        <v>1</v>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19005,12 +19097,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -19035,12 +19127,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N106" t="n">
@@ -19049,7 +19141,7 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
+      <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
@@ -19060,68 +19152,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -19148,17 +19249,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -19183,12 +19284,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N107" t="n">
@@ -19197,76 +19298,168 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN107" t="b">
+        <v>1</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -19328,12 +19521,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N108" t="n">
@@ -19443,12 +19636,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -19473,12 +19666,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N109" t="n">
@@ -19487,9 +19680,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="P109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19498,77 +19688,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19595,7 +19776,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -19630,12 +19811,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N110" t="n">
@@ -19647,98 +19828,18 @@
       <c r="P110" t="n">
         <v>0</v>
       </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD110" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE110" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG110" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN110" t="b">
-        <v>1</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -19832,17 +19933,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -19867,12 +19968,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N111" t="n">
@@ -19881,76 +19982,168 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="R111" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN111" t="b">
+        <v>1</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -19982,12 +20175,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -20012,7 +20205,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -20026,7 +20219,7 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="P112" t="n">
+      <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
@@ -20037,77 +20230,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -20134,17 +20318,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20169,7 +20353,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -20183,168 +20367,87 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="P113" t="n">
-        <v>0</v>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD113" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE113" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF113" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG113" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN113" t="b">
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
+        </is>
+      </c>
+      <c r="AT113" t="n">
         <v>1</v>
       </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP113" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="AT113" t="n">
-        <v>2</v>
-      </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -20371,17 +20474,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20406,7 +20509,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -20420,76 +20523,165 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="R114" t="n">
-        <v>0</v>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Official provincial report count for Ebola virus disease; source month is retained and absent rows remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>1</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_EBOLA</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -20521,12 +20713,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20551,7 +20743,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -20565,9 +20757,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20576,77 +20765,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20673,17 +20853,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20708,7 +20888,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -20722,168 +20902,76 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG116" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN116" t="b">
-        <v>1</v>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20915,12 +21003,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20945,7 +21033,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -20959,6 +21047,9 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -20967,68 +21058,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21155,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -21090,7 +21190,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -21107,18 +21207,98 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -21212,17 +21392,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21247,7 +21427,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -21261,168 +21441,76 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG119" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN119" t="b">
-        <v>1</v>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21454,12 +21542,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -21484,7 +21572,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -21498,6 +21586,9 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -21506,68 +21597,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21694,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -21629,7 +21729,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -21646,18 +21746,98 @@
       <c r="P121" t="n">
         <v>0</v>
       </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -21751,17 +21931,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21786,7 +21966,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -21800,168 +21980,76 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21993,12 +22081,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -22023,12 +22111,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N123" t="n">
@@ -22037,6 +22125,9 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -22045,68 +22136,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22133,17 +22233,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -22168,12 +22268,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N124" t="n">
@@ -22182,76 +22282,168 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22283,12 +22475,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -22313,12 +22505,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N125" t="n">
@@ -22327,9 +22519,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22338,77 +22527,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22435,7 +22615,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -22470,12 +22650,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N126" t="n">
@@ -22487,98 +22667,18 @@
       <c r="P126" t="n">
         <v>0</v>
       </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -22672,17 +22772,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22707,12 +22807,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N127" t="n">
@@ -22721,76 +22821,168 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22822,12 +23014,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22852,12 +23044,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N128" t="n">
@@ -22866,9 +23058,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -22877,77 +23066,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22974,7 +23154,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -23009,12 +23189,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N129" t="n">
@@ -23026,98 +23206,18 @@
       <c r="P129" t="n">
         <v>0</v>
       </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>Ebola Virus Disease</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE129" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG129" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN129" t="b">
-        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -23183,6 +23283,1466 @@
         </is>
       </c>
       <c r="BC129" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN130" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr"/>
+      <c r="AT132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN134" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -23304,7 +24864,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -23314,7 +24874,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -23334,7 +24894,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -23344,7 +24904,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d050/2026-2029.xlsx
+++ b/diseases/d050/2026-2029.xlsx
@@ -24748,6 +24748,690 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
+      <c r="AT138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN140" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
+      <c r="AT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24781,7 +25465,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -24864,7 +25548,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -24874,7 +25558,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -24894,7 +25578,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d050/2026-2029.xlsx
+++ b/diseases/d050/2026-2029.xlsx
@@ -25315,12 +25315,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -25345,12 +25345,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N141" t="n">
@@ -25393,40 +25393,185 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
+      <c r="AT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW141" t="inlineStr">
+      <c r="AW142" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX141" t="inlineStr">
+      <c r="AX142" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY141" t="inlineStr">
+      <c r="AY142" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ141" t="inlineStr">
+      <c r="AZ142" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA141" t="inlineStr">
+      <c r="BA142" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB141" t="inlineStr">
+      <c r="BB142" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC141" t="inlineStr">
+      <c r="BC142" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -25548,7 +25693,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -25558,7 +25703,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d050/2026-2029.xlsx
+++ b/diseases/d050/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3237,6 +3247,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3382,6 +3397,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5698,6 +5718,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5843,6 +5868,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8553,6 +8583,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8698,6 +8733,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11014,6 +11054,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11159,6 +11204,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14017,6 +14067,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14552,6 +14607,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16856,6 +16916,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17781,6 +17846,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20230,6 +20300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20765,6 +20840,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23605,6 +23685,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25460,118 +25545,517 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Ebola Virus Disease</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_EBOLA_VIRUS_DISEASE; SER_SG_HIST_EBOLA_VIRUS_DISEASE</t>
+        </is>
+      </c>
+      <c r="AT143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G144" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>D050</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Ebola</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
         <is>
           <t>埃博拉出血热</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="K144" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N142" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="inlineStr">
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO142" t="inlineStr">
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP142" t="inlineStr">
+      <c r="AP144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR142" t="inlineStr">
+      <c r="AR144" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS142" t="inlineStr"/>
-      <c r="AT142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV142" t="inlineStr">
+      <c r="AV144" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW142" t="inlineStr">
+      <c r="AW144" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX142" t="inlineStr">
+      <c r="AX144" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY142" t="inlineStr">
+      <c r="AY144" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ142" t="inlineStr">
+      <c r="AZ144" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA142" t="inlineStr">
+      <c r="BA144" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB142" t="inlineStr">
+      <c r="BB144" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC142" t="inlineStr">
+      <c r="BC144" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -25693,7 +26177,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -25703,7 +26187,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -25723,7 +26207,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d050/2026-2029.xlsx
+++ b/diseases/d050/2026-2029.xlsx
@@ -26061,6 +26061,151 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ebola</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D050</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Ebola</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>埃博拉出血热</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26094,7 +26239,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -26177,7 +26322,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -26187,7 +26332,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
